--- a/AutomationTestDemo/target/test-classes/LoginTestData.xlsx
+++ b/AutomationTestDemo/target/test-classes/LoginTestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{05155948-B033-41E6-AF6D-7B3CBF010905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{414CC9C7-728B-46C4-A231-F4A0C00A8CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12,12 +12,12 @@
     <sheet name="Messages" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="B10:J22"/>
+  <oleSize ref="A17:B21"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
   <si>
     <t>TestCase</t>
   </si>
@@ -162,6 +162,9 @@
   <si>
     <t>viewExistUsrDtl_13722</t>
   </si>
+  <si>
+    <t>deleteUserFromDetails_13735</t>
+  </si>
 </sst>
 </file>
 
@@ -279,7 +282,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -297,6 +300,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -28330,7 +28336,14 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:26" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:26" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
     <row r="20" spans="1:26" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="1:26" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:26" customFormat="1" x14ac:dyDescent="0.25"/>
